--- a/artfynd/A 33079-2024 artfynd.xlsx
+++ b/artfynd/A 33079-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126225005</v>
+        <v>126225006</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510090</v>
+        <v>510057</v>
       </c>
       <c r="R2" t="n">
-        <v>6755943</v>
+        <v>6755936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,6 +779,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126225005</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brunnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>510090</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6755943</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126225007</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brunnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>510076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6756015</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33079-2024 artfynd.xlsx
+++ b/artfynd/A 33079-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126225006</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126225005</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126225007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>